--- a/LoanOfficer-A/2023/119 dhanabir.xlsx
+++ b/LoanOfficer-A/2023/119 dhanabir.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD50000.15-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
@@ -400,7 +400,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -435,7 +435,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="G2" s="21">
         <f>B3+G1*7</f>
-        <v>119</v>
+        <v>45929</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11900</v>
+        <v>9100</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="1"/>
+      <c r="B3" s="3">
+        <v>45810</v>
+      </c>
+      <c r="C3" s="4">
+        <v>700</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
       <c r="E3" s="1">
         <v>31</v>
       </c>
@@ -900,9 +906,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45814</v>
+      </c>
+      <c r="C4" s="4">
+        <v>700</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -926,9 +938,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45827</v>
+      </c>
+      <c r="C5" s="4">
+        <v>700</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -952,9 +970,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45831</v>
+      </c>
+      <c r="C6" s="4">
+        <v>700</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>

--- a/LoanOfficer-A/2023/119 dhanabir.xlsx
+++ b/LoanOfficer-A/2023/119 dhanabir.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>2800</v>
+        <v>4900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>9100</v>
+        <v>7000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1002,9 +1002,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45844</v>
+      </c>
+      <c r="C7" s="4">
+        <v>700</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1028,9 +1034,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C8" s="4">
+        <v>700</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1054,9 +1066,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45851</v>
+      </c>
+      <c r="C9" s="4">
+        <v>700</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>

--- a/LoanOfficer-A/2023/119 dhanabir.xlsx
+++ b/LoanOfficer-A/2023/119 dhanabir.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>4900</v>
+        <v>5600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7000</v>
+        <v>6300</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1098,9 +1098,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45864</v>
+      </c>
+      <c r="C10" s="4">
+        <v>700</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>

--- a/LoanOfficer-A/2023/119 dhanabir.xlsx
+++ b/LoanOfficer-A/2023/119 dhanabir.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>5600</v>
+        <v>7700</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>6300</v>
+        <v>4200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1130,9 +1130,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45869</v>
+      </c>
+      <c r="C11" s="4">
+        <v>700</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1156,9 +1162,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45880</v>
+      </c>
+      <c r="C12" s="4">
+        <v>700</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1182,9 +1194,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45883</v>
+      </c>
+      <c r="C13" s="4">
+        <v>700</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>

--- a/LoanOfficer-A/2023/119 dhanabir.xlsx
+++ b/LoanOfficer-A/2023/119 dhanabir.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>7700</v>
+        <v>8400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1226,9 +1226,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C14" s="4">
+        <v>700</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>

--- a/LoanOfficer-A/2023/119 dhanabir.xlsx
+++ b/LoanOfficer-A/2023/119 dhanabir.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>8400</v>
+        <v>11900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1258,9 +1258,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C15" s="4">
+        <v>700</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1284,9 +1290,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45910</v>
+      </c>
+      <c r="C16" s="4">
+        <v>700</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1310,9 +1322,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45914</v>
+      </c>
+      <c r="C17" s="4">
+        <v>700</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1336,9 +1354,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45921</v>
+      </c>
+      <c r="C18" s="4">
+        <v>700</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1362,9 +1386,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45928</v>
+      </c>
+      <c r="C19" s="4">
+        <v>700</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
